--- a/artfynd/A 20601-2022 artfynd.xlsx
+++ b/artfynd/A 20601-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 20601-2022 artfynd.xlsx
+++ b/artfynd/A 20601-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2696,6 +2696,248 @@
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>125727733</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57453</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>102118</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Nattskärra</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Caprimulgus europaeus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Gröna dalen, Brunna, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>656207</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6599258</v>
+      </c>
+      <c r="S18" t="n">
+        <v>50</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Upplands-Bro</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Kungsängen</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>23:31</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>23:33</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Hygget motionsslingan.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Stefan Kyrklund</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Stefan Kyrklund, Iréne Kyrklund</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>125743636</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58129</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Gröna dalen, Brunna, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>656207</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6599258</v>
+      </c>
+      <c r="S19" t="n">
+        <v>50</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Upplands-Bro</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Kungsängen</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Stefan Kyrklund</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Stefan Kyrklund, Iréne Kyrklund</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20601-2022 artfynd.xlsx
+++ b/artfynd/A 20601-2022 artfynd.xlsx
@@ -2827,7 +2827,7 @@
         <v>125743636</v>
       </c>
       <c r="B19" t="n">
-        <v>58129</v>
+        <v>58130</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 20601-2022 artfynd.xlsx
+++ b/artfynd/A 20601-2022 artfynd.xlsx
@@ -2701,7 +2701,7 @@
         <v>125727733</v>
       </c>
       <c r="B18" t="n">
-        <v>57453</v>
+        <v>57454</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>125743636</v>
       </c>
       <c r="B19" t="n">
-        <v>58130</v>
+        <v>58131</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Stefan Kyrklund, Iréne Kyrklund</t>
+          <t>Iréne Kyrklund, Stefan Kyrklund</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 20601-2022 artfynd.xlsx
+++ b/artfynd/A 20601-2022 artfynd.xlsx
@@ -2933,7 +2933,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Iréne Kyrklund, Stefan Kyrklund</t>
+          <t>Stefan Kyrklund, Iréne Kyrklund</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 20601-2022 artfynd.xlsx
+++ b/artfynd/A 20601-2022 artfynd.xlsx
@@ -2701,7 +2701,7 @@
         <v>125727733</v>
       </c>
       <c r="B18" t="n">
-        <v>57454</v>
+        <v>57458</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>125743636</v>
       </c>
       <c r="B19" t="n">
-        <v>58131</v>
+        <v>58135</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
